--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,105 +459,110 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>roma_fonte_preco</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>roma_disponivel</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>conc_disponivel</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>conc_estoque_qtd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>situacao_estoque</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>roma_preco_cheio</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>roma_preco_pix</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>roma_preco_parcelado</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>roma_n_parcelas</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>roma_valor_parcela</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>nome_anuncio_concorrente</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>conc_preco_cheio</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>conc_preco_pix</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>conc_preco_parcelado</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>conc_n_parcelas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>conc_valor_parcela</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>conc_desconto_pix_pct</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>conc_desconto_parcelado_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>dif_pix_pct</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>dif_parcelado_pct</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>dif_parcela_pct</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>classificacao_pix</t>
         </is>
@@ -587,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -602,7 +607,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -610,65 +615,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>8</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>306.81</v>
-      </c>
-      <c r="N2" t="n">
-        <v>288.4</v>
       </c>
       <c r="O2" t="n">
         <v>288.4</v>
       </c>
       <c r="P2" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="Q2" t="n">
         <v>6</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>48.07</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Pneu 175/65R14 Goodyear Kelly Edge Touring 2 86H</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>348.85</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>306.99</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>348.85</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>12</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>29.07</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.1199942668768812</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-0.06055571842731045</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>-0.1732836462663037</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.65359477124183</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -698,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -713,7 +723,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -721,65 +731,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
         <v>8</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>423.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>397.68</v>
       </c>
       <c r="O3" t="n">
         <v>397.68</v>
       </c>
       <c r="P3" t="n">
+        <v>397.68</v>
+      </c>
+      <c r="Q3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>66.28</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Pneu 185/60R15 Goodyear Kelly Edge Sport 2 88H</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>447.72</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>393.99</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>447.72</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>12</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>37.31</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.1200080407397481</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.009365719942130424</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>-0.1117662824979898</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.7764674350040204</v>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -809,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -824,7 +839,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -832,65 +847,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>8</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>619.29</v>
-      </c>
-      <c r="N4" t="n">
-        <v>582.13</v>
       </c>
       <c r="O4" t="n">
         <v>582.13</v>
       </c>
       <c r="P4" t="n">
+        <v>582.13</v>
+      </c>
+      <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>97.02</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Pneu 205/65R16 Goodyear Efficientgrip SUV 95H Original Hyundai Creta</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>713.63</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>627.99</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>713.63</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>12</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>59.47</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>0.1200061656600759</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.07302664055160113</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>-0.1842691590880429</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>0.6314107953590045</v>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -920,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -935,7 +955,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -943,65 +963,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>8</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>353.31</v>
-      </c>
-      <c r="N5" t="n">
-        <v>332.11</v>
       </c>
       <c r="O5" t="n">
         <v>332.11</v>
       </c>
       <c r="P5" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>55.35</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Pneu 175/65R14 Goodyear Assurance Maxlife 86H</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>390.9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>343.99</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>390.9</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>12</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>32.57</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.1200051163980557</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.03453588767115323</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>-0.150396520849322</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>0.6994166410807492</v>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -1031,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1046,7 +1071,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1054,65 +1079,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>8</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>297.51</v>
-      </c>
-      <c r="N6" t="n">
-        <v>279.66</v>
       </c>
       <c r="O6" t="n">
         <v>279.66</v>
       </c>
       <c r="P6" t="n">
+        <v>279.66</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>46.61</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Pneu 175/70R13 Goodyear Kelly Edge Touring 2 82T</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>328.4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>288.99</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>328.4</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>12</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>27.37</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>0.1200060901339829</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>-0.03228485414720228</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>-0.1484165651644335</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>0.7029594446474241</v>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -1142,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1157,7 +1187,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1165,65 +1195,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>8</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>433.29</v>
-      </c>
-      <c r="N7" t="n">
-        <v>407.29</v>
       </c>
       <c r="O7" t="n">
         <v>407.29</v>
       </c>
       <c r="P7" t="n">
+        <v>407.29</v>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>67.88</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Pneu 185/65R15 Goodyear Kelly Edge Sport 2 88H</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>476.13</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>418.99</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>476.13</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>12</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>39.68</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>0.120009241173629</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-0.02792429413589825</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>-0.1445823619599689</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>0.7106854838709677</v>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -1253,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1268,36 +1303,40 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1097.31</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1031.47</v>
       </c>
       <c r="O8" t="n">
         <v>1031.47</v>
       </c>
       <c r="P8" t="n">
+        <v>1031.47</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>171.91</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1308,7 +1347,8 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Concorrente sem estoque</t>
         </is>
@@ -1338,7 +1378,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1353,7 +1393,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1361,65 +1401,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>702.99</v>
-      </c>
-      <c r="N9" t="n">
-        <v>660.8099999999999</v>
       </c>
       <c r="O9" t="n">
         <v>660.8099999999999</v>
       </c>
       <c r="P9" t="n">
+        <v>660.8099999999999</v>
+      </c>
+      <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>110.14</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Pneu 215/55R17 Goodyear Efficientgrip SUV 94V</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>724.99</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>637.99</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>724.99</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>12</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>60.42</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.1200016551952441</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>0.03576858571450958</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>-0.08852535897046865</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>0.8229063224097981</v>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -1449,7 +1494,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1464,7 +1509,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1472,65 +1517,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
         <v>8</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>353.31</v>
-      </c>
-      <c r="N10" t="n">
-        <v>332.11</v>
       </c>
       <c r="O10" t="n">
         <v>332.11</v>
       </c>
       <c r="P10" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="Q10" t="n">
         <v>6</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>55.35</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Pneu 175/70R13 Goodyear Assurance Maxlife 82T</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>424.99</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>373.99</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>424.99</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>12</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>35.42</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>0.1200028235958494</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-0.1119816037861975</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>-0.2185463187369114</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.5626764539808018</v>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -1560,7 +1610,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1575,73 +1625,78 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>planilha</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Risco: só o concorrente tem</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>463.05</v>
-      </c>
-      <c r="N11" t="n">
-        <v>435.27</v>
       </c>
       <c r="O11" t="n">
         <v>435.27</v>
       </c>
       <c r="P11" t="n">
+        <v>435.27</v>
+      </c>
+      <c r="Q11" t="n">
         <v>6</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>72.54000000000001</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Pneu 195/65R15 Goodyear Kelly Edge Sport 2 91V</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>498.85</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>438.99</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>498.85</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>12</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>41.57</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.1199959907787912</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>-0.008473997129775257</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>-0.1274531422271225</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>0.7450084195333175</v>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -1671,7 +1726,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1686,7 +1741,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1694,65 +1749,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>8</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>427.71</v>
-      </c>
-      <c r="N12" t="n">
-        <v>402.05</v>
       </c>
       <c r="O12" t="n">
         <v>402.05</v>
       </c>
       <c r="P12" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="Q12" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Pneu 205/55R16 Goodyear Kelly Edge Sport 2 91V</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>452.26</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>397.99</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>452.26</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>12</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>37.69</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.1199973466590014</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>0.01020126133822452</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>-0.1110202096139389</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>0.7779251790925978</v>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -1782,7 +1842,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1797,7 +1857,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1805,65 +1865,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
         <v>8</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>368.19</v>
-      </c>
-      <c r="N13" t="n">
-        <v>346.1</v>
       </c>
       <c r="O13" t="n">
         <v>346.1</v>
       </c>
       <c r="P13" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="Q13" t="n">
         <v>6</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>57.68</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>Pneu 175/70R14 Goodyear Kelly Edge Touring 2 88T</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>429.53</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>377.99</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>429.53</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>12</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>35.79</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>0.1199916187460712</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-0.08436731130453179</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>-0.1942355597979185</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>0.6116233584800224</v>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -1893,7 +1958,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1908,7 +1973,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1916,65 +1981,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>492.81</v>
-      </c>
-      <c r="N14" t="n">
-        <v>463.24</v>
       </c>
       <c r="O14" t="n">
         <v>463.24</v>
       </c>
       <c r="P14" t="n">
+        <v>463.24</v>
+      </c>
+      <c r="Q14" t="n">
         <v>6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>77.20999999999999</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Pneu 225/45R17 Goodyear Kelly Edge Sport 2 91W</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>568.17</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>499.99</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>568.17</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>12</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>47.35</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>0.1199992959853564</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>-0.07350147002940055</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>-0.1846806413573402</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>0.6306230200633578</v>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -2004,7 +2074,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2019,7 +2089,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2027,65 +2097,70 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
         <v>8</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>557.91</v>
-      </c>
-      <c r="N15" t="n">
-        <v>524.4400000000001</v>
       </c>
       <c r="O15" t="n">
         <v>524.4400000000001</v>
       </c>
       <c r="P15" t="n">
+        <v>524.4400000000001</v>
+      </c>
+      <c r="Q15" t="n">
         <v>6</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>87.41</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Pneu 195/55R16 Goodyear EfficientGrip Performance 91V</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>617.03</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>542.99</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>617.03</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>12</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>51.42</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>0.1199941655997276</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>-0.03416269176227915</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>-0.1500575336693515</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>0.6999222092570982</v>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -2115,7 +2190,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2130,7 +2205,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2138,63 +2213,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>306.81</v>
-      </c>
-      <c r="N16" t="n">
-        <v>288.4</v>
       </c>
       <c r="O16" t="n">
         <v>288.4</v>
       </c>
       <c r="P16" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="Q16" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>48.07</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 14 Edge Touring 2 175/65R14 86H XL</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>355.45</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>319.9</v>
       </c>
-      <c r="U16" t="n">
-        <v>342.47</v>
-      </c>
       <c r="V16" t="n">
-        <v>12</v>
+        <v>355.45</v>
       </c>
       <c r="W16" t="n">
-        <v>28.53</v>
+        <v>10</v>
       </c>
       <c r="X16" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="Y16" t="n">
         <v>0.1000140666760445</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0.03651709101139389</v>
-      </c>
       <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>-0.09846827133479208</v>
       </c>
-      <c r="AA16" t="n">
-        <v>-0.1578824422577161</v>
-      </c>
       <c r="AB16" t="n">
-        <v>0.6848930949877321</v>
-      </c>
-      <c r="AC16" t="inlineStr">
+        <v>-0.1886341257560838</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.3525604952166572</v>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -2224,7 +2304,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2239,7 +2319,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2247,63 +2327,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>423.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>397.68</v>
       </c>
       <c r="O17" t="n">
         <v>397.68</v>
       </c>
       <c r="P17" t="n">
+        <v>397.68</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>66.28</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 15 Edge Sport 2 185/60R15 88H XL</t>
         </is>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>481.59</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>394.9</v>
       </c>
-      <c r="U17" t="n">
-        <v>464.01</v>
-      </c>
       <c r="V17" t="n">
-        <v>12</v>
+        <v>481.59</v>
       </c>
       <c r="W17" t="n">
-        <v>38.66</v>
+        <v>10</v>
       </c>
       <c r="X17" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.1800078905292885</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0.03650408023422413</v>
-      </c>
       <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0.007039756900481198</v>
       </c>
-      <c r="AA17" t="n">
-        <v>-0.1429495053985905</v>
-      </c>
       <c r="AB17" t="n">
-        <v>0.7144335230212107</v>
-      </c>
-      <c r="AC17" t="inlineStr">
+        <v>-0.1742353454183018</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.3765316718587748</v>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -2333,7 +2418,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2348,7 +2433,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2356,63 +2441,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>619.29</v>
-      </c>
-      <c r="N18" t="n">
-        <v>582.13</v>
       </c>
       <c r="O18" t="n">
         <v>582.13</v>
       </c>
       <c r="P18" t="n">
+        <v>582.13</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>97.02</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>Pneu Goodyear Aro 16 EfficientGrip SUV 205/65R16 95H</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>755.45</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>679.9</v>
       </c>
-      <c r="U18" t="n">
-        <v>727.87</v>
-      </c>
       <c r="V18" t="n">
-        <v>12</v>
+        <v>755.45</v>
       </c>
       <c r="W18" t="n">
-        <v>60.65</v>
+        <v>10</v>
       </c>
       <c r="X18" t="n">
+        <v>75.54000000000001</v>
+      </c>
+      <c r="Y18" t="n">
         <v>0.1000066185717123</v>
       </c>
-      <c r="Y18" t="n">
-        <v>0.03650804156463039</v>
-      </c>
       <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
         <v>-0.1438005589057214</v>
       </c>
-      <c r="AA18" t="n">
-        <v>-0.2002280627035048</v>
-      </c>
       <c r="AB18" t="n">
-        <v>0.5996702390766693</v>
-      </c>
-      <c r="AC18" t="inlineStr">
+        <v>-0.2294261698325502</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.2843526608419378</v>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -2442,7 +2532,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2457,7 +2547,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2465,63 +2555,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>353.31</v>
-      </c>
-      <c r="N19" t="n">
-        <v>332.11</v>
       </c>
       <c r="O19" t="n">
         <v>332.11</v>
       </c>
       <c r="P19" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="Q19" t="n">
         <v>6</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>55.35</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>Pneu Goodyear Aro 14 Assurance Maxlife 175/65R14 86H XL</t>
         </is>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>397.62</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>349.9</v>
       </c>
-      <c r="U19" t="n">
-        <v>383.1</v>
-      </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>397.62</v>
       </c>
       <c r="W19" t="n">
-        <v>31.92</v>
+        <v>10</v>
       </c>
       <c r="X19" t="n">
+        <v>39.76</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.1200140837986018</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0.03651727780292735</v>
-      </c>
       <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
         <v>-0.0508430980280079</v>
       </c>
-      <c r="AA19" t="n">
-        <v>-0.1330984077264422</v>
-      </c>
       <c r="AB19" t="n">
-        <v>0.7340225563909775</v>
-      </c>
-      <c r="AC19" t="inlineStr">
+        <v>-0.1647552939992958</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.3921026156941652</v>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -2551,7 +2646,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2566,7 +2661,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2574,63 +2669,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>297.51</v>
-      </c>
-      <c r="N20" t="n">
-        <v>279.66</v>
       </c>
       <c r="O20" t="n">
         <v>279.66</v>
       </c>
       <c r="P20" t="n">
+        <v>279.66</v>
+      </c>
+      <c r="Q20" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>46.61</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 13 Edge Touring 2 175/70R13 82T</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>333.23</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>299.9</v>
       </c>
-      <c r="U20" t="n">
-        <v>321.06</v>
-      </c>
       <c r="V20" t="n">
-        <v>12</v>
+        <v>333.23</v>
       </c>
       <c r="W20" t="n">
-        <v>26.75</v>
+        <v>10</v>
       </c>
       <c r="X20" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.1000210065120188</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0.03652132160969901</v>
-      </c>
       <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>-0.06748916305435126</v>
       </c>
-      <c r="AA20" t="n">
-        <v>-0.1289478602130443</v>
-      </c>
       <c r="AB20" t="n">
-        <v>0.7424299065420561</v>
-      </c>
-      <c r="AC20" t="inlineStr">
+        <v>-0.1607598355490202</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.3988595438175271</v>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -2660,7 +2760,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2675,7 +2775,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2683,63 +2783,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>433.29</v>
-      </c>
-      <c r="N21" t="n">
-        <v>407.29</v>
       </c>
       <c r="O21" t="n">
         <v>407.29</v>
       </c>
       <c r="P21" t="n">
+        <v>407.29</v>
+      </c>
+      <c r="Q21" t="n">
         <v>6</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>67.88</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 15 Edge Sport 2 185/65R15 88H</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>512.08</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>419.9</v>
       </c>
-      <c r="U21" t="n">
-        <v>493.38</v>
-      </c>
       <c r="V21" t="n">
-        <v>12</v>
+        <v>512.08</v>
       </c>
       <c r="W21" t="n">
-        <v>41.11</v>
+        <v>10</v>
       </c>
       <c r="X21" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="Y21" t="n">
         <v>0.1800109357912827</v>
       </c>
-      <c r="Y21" t="n">
-        <v>0.03651773160443694</v>
-      </c>
       <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
         <v>-0.03003095975232184</v>
       </c>
-      <c r="AA21" t="n">
-        <v>-0.17449025092221</v>
-      </c>
       <c r="AB21" t="n">
-        <v>0.6511797616151787</v>
-      </c>
-      <c r="AC21" t="inlineStr">
+        <v>-0.2046359943758788</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.3257812499999999</v>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -2769,7 +2874,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2784,41 +2889,45 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>1097.31</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1031.47</v>
       </c>
       <c r="O22" t="n">
         <v>1031.47</v>
       </c>
       <c r="P22" t="n">
+        <v>1031.47</v>
+      </c>
+      <c r="Q22" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>171.91</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>Pneu Goodyear Aro 16 Cargo Marathon 2 225/75R16C 118R 10 Lonas</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2828,7 +2937,8 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr">
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>Concorrente sem estoque</t>
         </is>
@@ -2858,7 +2968,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2873,7 +2983,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>planilha</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2881,63 +2991,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>702.99</v>
-      </c>
-      <c r="N23" t="n">
-        <v>660.8099999999999</v>
       </c>
       <c r="O23" t="n">
         <v>660.8099999999999</v>
       </c>
       <c r="P23" t="n">
+        <v>660.8099999999999</v>
+      </c>
+      <c r="Q23" t="n">
         <v>6</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>110.14</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Pneu Goodyear Aro 17 EfficientGrip SUV 215/55R17 94V</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>749.89</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>674.9</v>
       </c>
-      <c r="U23" t="n">
-        <v>722.51</v>
-      </c>
       <c r="V23" t="n">
-        <v>12</v>
+        <v>749.89</v>
       </c>
       <c r="W23" t="n">
-        <v>60.2</v>
+        <v>10</v>
       </c>
       <c r="X23" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0.1000013335289176</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0.0365120217631919</v>
-      </c>
       <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
         <v>-0.02087716698770192</v>
       </c>
-      <c r="AA23" t="n">
-        <v>-0.0853967419136068</v>
-      </c>
       <c r="AB23" t="n">
-        <v>0.8295681063122924</v>
-      </c>
-      <c r="AC23" t="inlineStr">
+        <v>-0.1187907559775434</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.4689250466791144</v>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -2967,7 +3082,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2982,7 +3097,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2990,63 +3105,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>353.31</v>
-      </c>
-      <c r="N24" t="n">
-        <v>332.11</v>
       </c>
       <c r="O24" t="n">
         <v>332.11</v>
       </c>
       <c r="P24" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="Q24" t="n">
         <v>6</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>55.35</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Pneu Goodyear Aro 13 Assurance Maxlife 175/70R13 82T</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>426.03</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>374.9</v>
       </c>
-      <c r="U24" t="n">
-        <v>410.47</v>
-      </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>426.03</v>
       </c>
       <c r="W24" t="n">
-        <v>34.2</v>
+        <v>10</v>
       </c>
       <c r="X24" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.1200150224162617</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0.0365232495364175</v>
-      </c>
       <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
         <v>-0.1141371032275272</v>
       </c>
-      <c r="AA24" t="n">
-        <v>-0.1909031110678003</v>
-      </c>
       <c r="AB24" t="n">
-        <v>0.6184210526315788</v>
-      </c>
-      <c r="AC24" t="inlineStr">
+        <v>-0.2204539586414102</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.2992957746478873</v>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -3076,7 +3196,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3091,71 +3211,76 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>planilha</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>nao</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
         <is>
           <t>Risco: só o concorrente tem</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>463.05</v>
-      </c>
-      <c r="N25" t="n">
-        <v>435.27</v>
       </c>
       <c r="O25" t="n">
         <v>435.27</v>
       </c>
       <c r="P25" t="n">
+        <v>435.27</v>
+      </c>
+      <c r="Q25" t="n">
         <v>6</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>72.54000000000001</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 15 Edge Sport 2 195/65R15 91V</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>536.47</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>439.9</v>
       </c>
-      <c r="U25" t="n">
-        <v>516.88</v>
-      </c>
       <c r="V25" t="n">
-        <v>12</v>
+        <v>536.47</v>
       </c>
       <c r="W25" t="n">
-        <v>43.07</v>
+        <v>10</v>
       </c>
       <c r="X25" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0.1800100658005108</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0.03651648740842928</v>
-      </c>
       <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
         <v>-0.01052511934530576</v>
       </c>
-      <c r="AA25" t="n">
-        <v>-0.157889645565702</v>
-      </c>
       <c r="AB25" t="n">
-        <v>0.6842349663338751</v>
-      </c>
-      <c r="AC25" t="inlineStr">
+        <v>-0.1886405577199098</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.3523489932885908</v>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -3185,7 +3310,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3200,7 +3325,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3208,63 +3333,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>427.71</v>
-      </c>
-      <c r="N26" t="n">
-        <v>402.05</v>
       </c>
       <c r="O26" t="n">
         <v>402.05</v>
       </c>
       <c r="P26" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="Q26" t="n">
         <v>6</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>67.01000000000001</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 16 Edge Sport 2 205/55R16 91V</t>
         </is>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>444.33</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>399.89</v>
       </c>
-      <c r="U26" t="n">
-        <v>428.11</v>
-      </c>
       <c r="V26" t="n">
-        <v>12</v>
+        <v>444.33</v>
       </c>
       <c r="W26" t="n">
-        <v>35.67</v>
+        <v>10</v>
       </c>
       <c r="X26" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.1000157540566696</v>
       </c>
-      <c r="Y26" t="n">
-        <v>0.03650439988296983</v>
-      </c>
       <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>0.005401485408487394</v>
       </c>
-      <c r="AA26" t="n">
-        <v>-0.06087220574151508</v>
-      </c>
       <c r="AB26" t="n">
-        <v>0.8786094757499299</v>
-      </c>
-      <c r="AC26" t="inlineStr">
+        <v>-0.09515450228433819</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.5082151699302275</v>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>Na média</t>
         </is>
@@ -3294,7 +3424,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3309,7 +3439,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3317,63 +3447,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>368.19</v>
-      </c>
-      <c r="N27" t="n">
-        <v>346.1</v>
       </c>
       <c r="O27" t="n">
         <v>346.1</v>
       </c>
       <c r="P27" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="Q27" t="n">
         <v>6</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>57.68</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 14 Edge Touring 2 175/70R14 88T XL</t>
         </is>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>433.23</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>389.9</v>
       </c>
-      <c r="U27" t="n">
-        <v>417.41</v>
-      </c>
       <c r="V27" t="n">
-        <v>12</v>
+        <v>433.23</v>
       </c>
       <c r="W27" t="n">
-        <v>34.78</v>
+        <v>10</v>
       </c>
       <c r="X27" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0.1000161576991437</v>
       </c>
-      <c r="Y27" t="n">
-        <v>0.03651640006463075</v>
-      </c>
       <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>-0.1123364965375736</v>
       </c>
-      <c r="AA27" t="n">
-        <v>-0.1708392228264776</v>
-      </c>
       <c r="AB27" t="n">
-        <v>0.6584243818286371</v>
-      </c>
-      <c r="AC27" t="inlineStr">
+        <v>-0.2011171894836461</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.3314866112650046</v>
+      </c>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -3403,7 +3538,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3418,7 +3553,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3426,63 +3561,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>492.81</v>
-      </c>
-      <c r="N28" t="n">
-        <v>463.24</v>
       </c>
       <c r="O28" t="n">
         <v>463.24</v>
       </c>
       <c r="P28" t="n">
+        <v>463.24</v>
+      </c>
+      <c r="Q28" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>77.20999999999999</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Pneu Kelly by Goodyear Aro 17 Edge Sport 2 225/45R17 91W</t>
         </is>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>555.45</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>499.9</v>
       </c>
-      <c r="U28" t="n">
-        <v>535.17</v>
-      </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>555.45</v>
       </c>
       <c r="W28" t="n">
-        <v>44.59</v>
+        <v>10</v>
       </c>
       <c r="X28" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="Y28" t="n">
         <v>0.1000090017103251</v>
       </c>
-      <c r="Y28" t="n">
-        <v>0.03651093707804498</v>
-      </c>
       <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>-0.07333466693338664</v>
       </c>
-      <c r="AA28" t="n">
-        <v>-0.1344058897172861</v>
-      </c>
       <c r="AB28" t="n">
-        <v>0.7315541601255884</v>
-      </c>
-      <c r="AC28" t="inlineStr">
+        <v>-0.1660095418129445</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0.3901692473892688</v>
+      </c>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>
@@ -3512,7 +3652,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-05 11:36</t>
+          <t>2026-10-07 15:43</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3527,7 +3667,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3535,63 +3675,68 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
         <is>
           <t>Ambos têm</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>557.91</v>
-      </c>
-      <c r="N29" t="n">
-        <v>524.4400000000001</v>
       </c>
       <c r="O29" t="n">
         <v>524.4400000000001</v>
       </c>
       <c r="P29" t="n">
+        <v>524.4400000000001</v>
+      </c>
+      <c r="Q29" t="n">
         <v>6</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>87.41</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Pneu Goodyear Aro 16 EfficientGrip Performance EV 195/55R16 91V XL</t>
         </is>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>999.89</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>899.9</v>
       </c>
-      <c r="U29" t="n">
-        <v>963.39</v>
-      </c>
       <c r="V29" t="n">
-        <v>12</v>
+        <v>999.89</v>
       </c>
       <c r="W29" t="n">
-        <v>80.28</v>
+        <v>10</v>
       </c>
       <c r="X29" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="Y29" t="n">
         <v>0.1000010001100121</v>
       </c>
-      <c r="Y29" t="n">
-        <v>0.03650401544169857</v>
-      </c>
       <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
         <v>-0.4172241360151128</v>
       </c>
-      <c r="AA29" t="n">
-        <v>-0.4556306376441523</v>
-      </c>
       <c r="AB29" t="n">
-        <v>0.08881415047334329</v>
-      </c>
-      <c r="AC29" t="inlineStr">
+        <v>-0.4755023052535778</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-0.1257251450290059</v>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>Competitivo</t>
         </is>

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-07 15:43</t>
+          <t>2026-10-09 13:18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mesmo produto</t>
+          <t>alternativo (Cargo Marathon 3)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1313,13 +1313,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>nao</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>8</v>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Oportunidade: só a Roma tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1337,20 +1339,44 @@
       <c r="R8" t="n">
         <v>171.91</v>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Pneu 225/75R16C Goodyear Cargo Marathon 3 118/116R</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>1306.81</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1149.99</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1306.81</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1200021426221103</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.1030617657544848</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.2106962756636389</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5786042240587694</v>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Concorrente sem estoque</t>
+          <t>Competitivo</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1494,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1610,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1726,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1842,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1958,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2074,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2190,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2304,7 +2330,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2418,7 +2444,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2532,7 +2558,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2646,7 +2672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2760,7 +2786,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2874,7 +2900,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2968,7 +2994,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3082,7 +3108,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3196,7 +3222,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3310,7 +3336,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3424,7 +3450,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3538,7 +3564,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3652,7 +3678,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-09 13:18</t>
+          <t>2026-10-09 13:48</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3662,7 +3688,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>alternativo (EV)</t>
+          <t>mesmo produto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3703,42 +3729,42 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Pneu Goodyear Aro 16 EfficientGrip Performance EV 195/55R16 91V XL</t>
+          <t>Pneu Goodyear Aro 16 EfficientGrip Performance 195/55R16 91V XL</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>999.89</v>
+        <v>599.89</v>
       </c>
       <c r="U29" t="n">
-        <v>899.9</v>
+        <v>539.9</v>
       </c>
       <c r="V29" t="n">
-        <v>999.89</v>
+        <v>599.89</v>
       </c>
       <c r="W29" t="n">
         <v>10</v>
       </c>
       <c r="X29" t="n">
-        <v>99.98</v>
+        <v>59.98</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1000010001100121</v>
+        <v>0.1000016669722783</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.4172241360151128</v>
+        <v>-0.02863493239488779</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.4755023052535778</v>
+        <v>-0.1257730583940389</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.1257251450290059</v>
+        <v>0.4573191063687896</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Na média</t>
         </is>
       </c>
     </row>

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Risco: só o concorrente tem</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2041,38 +2041,38 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>568.17</v>
+        <v>543.17</v>
       </c>
       <c r="U14" t="n">
-        <v>499.99</v>
+        <v>477.99</v>
       </c>
       <c r="V14" t="n">
-        <v>568.17</v>
+        <v>543.17</v>
       </c>
       <c r="W14" t="n">
         <v>12</v>
       </c>
       <c r="X14" t="n">
-        <v>47.35</v>
+        <v>45.26</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1199992959853564</v>
+        <v>0.1199992635823038</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.07350147002940055</v>
+        <v>-0.03085838615870629</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.1846806413573402</v>
+        <v>-0.147154666126627</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.6306230200633578</v>
+        <v>0.7059213433495359</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Na média</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2157,34 +2157,34 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>617.03</v>
+        <v>612.49</v>
       </c>
       <c r="U15" t="n">
-        <v>542.99</v>
+        <v>538.99</v>
       </c>
       <c r="V15" t="n">
-        <v>617.03</v>
+        <v>612.49</v>
       </c>
       <c r="W15" t="n">
         <v>12</v>
       </c>
       <c r="X15" t="n">
-        <v>51.42</v>
+        <v>51.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1199941655997276</v>
+        <v>0.1200019592156607</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.03416269176227915</v>
+        <v>-0.02699493497096417</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1500575336693515</v>
+        <v>-0.1437574491012097</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.6999222092570982</v>
+        <v>0.712578369905956</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2241,13 +2241,13 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2270,39 +2270,19 @@
           <t>Pneu Kelly by Goodyear Aro 14 Edge Touring 2 175/65R14 86H XL</t>
         </is>
       </c>
-      <c r="T16" t="n">
-        <v>355.45</v>
-      </c>
-      <c r="U16" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>355.45</v>
-      </c>
-      <c r="W16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X16" t="n">
-        <v>35.54</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.1000140666760445</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.09846827133479208</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-0.1886341257560838</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.3525604952166572</v>
-      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2310,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2345,7 +2325,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2444,7 +2424,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2459,7 +2439,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2558,7 +2538,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2573,12 +2553,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2589,7 +2569,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Risco: só o concorrente tem</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -2672,7 +2652,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2687,7 +2667,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2697,13 +2677,13 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -2726,39 +2706,19 @@
           <t>Pneu Kelly by Goodyear Aro 13 Edge Touring 2 175/70R13 82T</t>
         </is>
       </c>
-      <c r="T20" t="n">
-        <v>333.23</v>
-      </c>
-      <c r="U20" t="n">
-        <v>299.9</v>
-      </c>
-      <c r="V20" t="n">
-        <v>333.23</v>
-      </c>
-      <c r="W20" t="n">
-        <v>10</v>
-      </c>
-      <c r="X20" t="n">
-        <v>33.32</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.1000210065120188</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>-0.06748916305435126</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-0.1607598355490202</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.3988595438175271</v>
-      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2746,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2801,7 +2761,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2900,7 +2860,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2915,7 +2875,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2994,7 +2954,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3009,7 +2969,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3108,7 +3068,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3163,34 +3123,34 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>426.03</v>
+        <v>431.7</v>
       </c>
       <c r="U24" t="n">
-        <v>374.9</v>
+        <v>379.89</v>
       </c>
       <c r="V24" t="n">
-        <v>426.03</v>
+        <v>431.7</v>
       </c>
       <c r="W24" t="n">
         <v>10</v>
       </c>
       <c r="X24" t="n">
-        <v>42.6</v>
+        <v>43.17</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1200150224162617</v>
+        <v>0.1200138985406533</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.1141371032275272</v>
+        <v>-0.1257732501513595</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.2204539586414102</v>
+        <v>-0.2306926106092193</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2992957746478873</v>
+        <v>0.2821403752605975</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3222,7 +3182,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3237,7 +3197,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>planilha</t>
+          <t>site</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3336,7 +3296,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3450,7 +3410,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3564,7 +3524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3678,7 +3638,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-09 13:48</t>
+          <t>2026-10-14 16:28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-14 16:28</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-15 13:42</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-15 13:42</t>
+          <t>2026-10-15 14:13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2241,13 +2241,13 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Oportunidade: só a Roma tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2270,19 +2270,39 @@
           <t>Pneu Kelly by Goodyear Aro 14 Edge Touring 2 175/65R14 86H XL</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10</v>
+      </c>
+      <c r="X16" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.1000140666760445</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.09846827133479208</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.1886341257560838</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.3525604952166572</v>
+      </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Concorrente sem estoque</t>
+          <t>Competitivo</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2330,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2424,7 +2444,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2538,7 +2558,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2652,7 +2672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2746,7 +2766,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2860,7 +2880,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2954,7 +2974,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3068,7 +3088,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3182,7 +3202,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3296,7 +3316,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3410,7 +3430,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3524,7 +3544,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3638,7 +3658,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-15 14:13</t>
+          <t>2026-10-16 11:42</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/base_concorrencia.xlsx
+++ b/base_concorrencia.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -649,38 +649,38 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>348.85</v>
+        <v>331.81</v>
       </c>
       <c r="U2" t="n">
-        <v>306.99</v>
+        <v>291.99</v>
       </c>
       <c r="V2" t="n">
-        <v>348.85</v>
+        <v>331.81</v>
       </c>
       <c r="W2" t="n">
         <v>12</v>
       </c>
       <c r="X2" t="n">
-        <v>29.07</v>
+        <v>27.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1199942668768812</v>
+        <v>0.1200084385642386</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.06055571842731045</v>
+        <v>-0.01229494160758937</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1732836462663037</v>
+        <v>-0.1308278834272627</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.65359477124183</v>
+        <v>0.7385171790235083</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Competitivo</t>
+          <t>Na média</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Risco: só o concorrente tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Risco: só o concorrente tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Risco: só o concorrente tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2999,13 +2999,13 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3028,39 +3028,19 @@
           <t>Pneu Goodyear Aro 17 EfficientGrip SUV 215/55R17 94V</t>
         </is>
       </c>
-      <c r="T23" t="n">
-        <v>749.89</v>
-      </c>
-      <c r="U23" t="n">
-        <v>674.9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>749.89</v>
-      </c>
-      <c r="W23" t="n">
-        <v>10</v>
-      </c>
-      <c r="X23" t="n">
-        <v>74.98</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.1000013335289176</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-0.02087716698770192</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>-0.1187907559775434</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.4689250466791144</v>
-      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Na média</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3068,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3202,7 +3182,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3222,7 +3202,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>nao</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3233,7 +3213,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Risco: só o concorrente tem</t>
+          <t>Ambos têm</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -3316,7 +3296,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3430,7 +3410,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3544,7 +3524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3658,7 +3638,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-16 11:42</t>
+          <t>2026-10-20 08:21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3683,13 +3663,13 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>nao</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ambos têm</t>
+          <t>Oportunidade: só a Roma tem</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -3712,39 +3692,19 @@
           <t>Pneu Goodyear Aro 16 EfficientGrip Performance 195/55R16 91V XL</t>
         </is>
       </c>
-      <c r="T29" t="n">
-        <v>599.89</v>
-      </c>
-      <c r="U29" t="n">
-        <v>539.9</v>
-      </c>
-      <c r="V29" t="n">
-        <v>599.89</v>
-      </c>
-      <c r="W29" t="n">
-        <v>10</v>
-      </c>
-      <c r="X29" t="n">
-        <v>59.98</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.1000016669722783</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>-0.02863493239488779</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-0.1257730583940389</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.4573191063687896</v>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Na média</t>
+          <t>Concorrente sem estoque</t>
         </is>
       </c>
     </row>
